--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128879471</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128879467</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128879471</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128879467</v>
       </c>
       <c r="B2" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128879471</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128879471</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128879466</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128879467</v>
+        <v>128879466</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storemossen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>331596</v>
+        <v>331375</v>
       </c>
       <c r="R2" t="n">
-        <v>6621966</v>
+        <v>6621917</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -784,11 +779,11 @@
         <v>128879471</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128879466</v>
+        <v>128879467</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +888,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storemossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>331375</v>
+        <v>331596</v>
       </c>
       <c r="R4" t="n">
-        <v>6621917</v>
+        <v>6621966</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 61527-2022 artfynd.xlsx
+++ b/artfynd/A 61527-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128879466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128879471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,8 +995,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128879467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>